--- a/artfynd/A 18399-2025 artfynd.xlsx
+++ b/artfynd/A 18399-2025 artfynd.xlsx
@@ -675,43 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72281102</v>
+        <v>109414477</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>208257</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623522.4949010145</v>
+        <v>623522</v>
       </c>
       <c r="R2" t="n">
-        <v>6943112.012236523</v>
+        <v>6943112</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Död med avbiten svans, ca 10 cm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,48 +787,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109414477</v>
+        <v>72281102</v>
       </c>
       <c r="B3" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>220204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623522.4949010145</v>
+        <v>623522</v>
       </c>
       <c r="R3" t="n">
-        <v>6943112.012236523</v>
+        <v>6943112</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,27 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Död med avbiten svans, ca 10 cm</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18399-2025 artfynd.xlsx
+++ b/artfynd/A 18399-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109414477</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72281102</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>